--- a/artfynd/A 50816-2025 artfynd.xlsx
+++ b/artfynd/A 50816-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136468792</v>
       </c>
       <c r="B4" t="n">
-        <v>43340</v>
+        <v>43342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
